--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-medication-dispense.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-medication-dispense.header.langue</t>
+    <t>fr-lm-medication-dispense.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-medication-dispense.completude</t>
@@ -499,7 +499,7 @@
     <t>fr-lm-medication-dispense.posologie</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dosage-instructions
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dosageInstructions
 </t>
   </si>
   <si>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -2496,7 +2490,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2547,31 +2541,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2585,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2614,10 +2608,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2668,7 +2662,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2685,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2714,10 +2708,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2768,7 +2762,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2785,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2814,10 +2808,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2847,10 +2841,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2868,7 +2862,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2885,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2911,13 +2905,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2968,7 +2962,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2985,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3011,13 +3005,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3068,7 +3062,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3085,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3111,13 +3105,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3168,7 +3162,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3185,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3211,13 +3205,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3268,7 +3262,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3285,10 +3279,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3311,13 +3305,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3368,7 +3362,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3385,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3414,10 +3408,10 @@
         <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3468,7 +3462,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3485,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3514,10 +3508,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3547,10 +3541,10 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3568,7 +3562,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -295,6 +295,9 @@
     <t>fr-lm-medication-dispense.header.author[x]</t>
   </si>
   <si>
+    <t>Auteur de la Auteur de la dispensation</t>
+  </si>
+  <si>
     <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
   </si>
   <si>
@@ -422,7 +425,16 @@
 </t>
   </si>
   <si>
+    <t>Statut de la ligne de prescription</t>
+  </si>
+  <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>Valeur issue du JDV_CompletudeDispensation_CISIS (1.2.250.1.213.1.1.5.765)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -448,49 +460,64 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-medication-dispense.completude</t>
-  </si>
-  <si>
-    <t>Complétude de la dispensation</t>
-  </si>
-  <si>
-    <t>Valeur issue du JDV_CompletudeDispensation_CISIS (1.2.250.1.213.1.1.5.765)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.quantite</t>
+    <t>fr-lm-medication-dispense.receiver[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person</t>
+  </si>
+  <si>
+    <t>Identification de la personne ayant reçu le médicament délivré, notamment lorsqu'il ne s'agit pas du patient. Si non présent, le patient est considéré comme le destinataire.</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.relatedRequest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {elementdefinition-identifier}
+</t>
+  </si>
+  <si>
+    <t>Référence de la prescription</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.medicament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
+</t>
+  </si>
+  <si>
+    <t>Médicament délivré</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.dispensedQuantity</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
-    <t>Quantité : Unité issue de EDQM Packaging</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.medicamentDelivre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
+    <t>Quantite de produit. 
+Nombre d'emballages distribués si leur format est connu, ou nombre d'articles/unités plus petits, selon le médicament distribué. Une unité est attendue.</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.timeOfDispensation</t>
+  </si>
+  <si>
+    <t>Date et heure de dispense du médicament. Si non présent, la date de dispensation est celle du header.</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.substitutionOccurred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>Médicament délivré</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.referencePrescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-reference-item-prescription
-</t>
-  </si>
-  <si>
-    <t>Référence de la prescription</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.posologie</t>
+    <t>Autorisation de substitution</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-dispense.dosageInstructions</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dosageInstructions
@@ -500,7 +527,7 @@
     <t>Posologie</t>
   </si>
   <si>
-    <t>fr-lm-medication-dispense.notesDispensateur</t>
+    <t>fr-lm-medication-dispense.note</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -508,24 +535,6 @@
   </si>
   <si>
     <t>Notes du dispensateur</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.autorisationSubstitution</t>
-  </si>
-  <si>
-    <t>Autorisation de substitution</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-dispense.autorisationSubstitution.type</t>
-  </si>
-  <si>
-    <t>Type de substitution jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis (2.16.840.1.113883.1.11.16621)</t>
-  </si>
-  <si>
-    <t>HL7_SubstanceAdminSubstitution</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis</t>
   </si>
 </sst>
 </file>
@@ -840,7 +849,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.41796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="143.30078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -855,7 +864,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.36328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.43359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1390,7 +1399,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>75</v>
@@ -1411,7 +1420,7 @@
         <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1462,7 +1471,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1479,10 +1488,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1505,13 +1514,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1562,7 +1571,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1579,10 +1588,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1605,13 +1614,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1662,7 +1671,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1679,10 +1688,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1705,13 +1714,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1762,7 +1771,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1779,10 +1788,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1805,13 +1814,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1862,7 +1871,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1879,10 +1888,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1908,10 +1917,10 @@
         <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1962,7 +1971,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1979,10 +1988,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2005,13 +2014,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2062,7 +2071,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2079,10 +2088,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2105,13 +2114,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2162,7 +2171,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2179,10 +2188,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2205,13 +2214,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2262,7 +2271,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2279,10 +2288,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2305,13 +2314,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2362,7 +2371,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2379,10 +2388,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2405,13 +2414,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2462,7 +2471,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2479,10 +2488,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2490,7 +2499,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2505,13 +2514,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2541,10 +2550,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2562,7 +2571,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2579,10 +2588,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2605,13 +2614,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2662,7 +2671,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2679,10 +2688,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2705,13 +2714,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2762,7 +2771,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2779,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2805,13 +2814,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2841,10 +2850,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2862,7 +2871,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2879,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2890,10 +2899,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2905,13 +2914,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2962,13 +2971,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
@@ -2979,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3005,13 +3014,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3062,7 +3071,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3079,10 +3088,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3090,7 +3099,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3105,13 +3114,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3162,10 +3171,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3179,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3205,13 +3214,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3262,7 +3271,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3279,10 +3288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3290,7 +3299,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3305,13 +3314,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3362,10 +3371,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3379,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3390,7 +3399,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3405,13 +3414,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3462,10 +3471,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3479,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3505,13 +3514,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3541,28 +3550,28 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
